--- a/Indiana_Pacers_2025-26_stats.xlsx
+++ b/Indiana_Pacers_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,50 +489,45 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Johnny Furphy</t>
+          <t>Tony Bradley</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Tony Bradley</t>
+          <t>Isaiah Jackson</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Isaiah Jackson</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Jay Huff</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
@@ -577,30 +572,27 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" t="n">
         <v>32</v>
       </c>
     </row>
@@ -643,30 +635,27 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -709,30 +698,27 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>6</v>
       </c>
-      <c r="O4" t="n">
-        <v>18</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="n">
         <v>33</v>
       </c>
     </row>
@@ -775,30 +761,27 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
         <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
         <v>5</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8</v>
-      </c>
       <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -841,30 +824,27 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
         <v>18</v>
       </c>
     </row>
@@ -904,33 +884,30 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -970,33 +947,30 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1036,33 +1010,30 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
+        <v>15</v>
+      </c>
+      <c r="O9" t="n">
         <v>8</v>
       </c>
-      <c r="O9" t="n">
-        <v>15</v>
-      </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
-      </c>
-      <c r="T9" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1102,33 +1073,30 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>4</v>
       </c>
-      <c r="O10" t="n">
-        <v>25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1168,33 +1136,30 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>12</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="n">
-        <v>12</v>
-      </c>
-      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1234,33 +1199,30 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1285,49 +1247,109 @@
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" t="n">
         <v>10</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
         <v>8</v>
       </c>
-      <c r="O13" t="n">
-        <v>10</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>19</v>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1341,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,50 +1419,45 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Johnny Furphy</t>
+          <t>Tony Bradley</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Tony Bradley</t>
+          <t>Isaiah Jackson</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Isaiah Jackson</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Jay Huff</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
@@ -1497,18 +1514,15 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1557,24 +1571,21 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1617,30 +1628,27 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1683,30 +1691,27 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1752,27 +1757,24 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1818,27 +1820,24 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1884,27 +1883,24 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1947,30 +1943,27 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2013,30 +2006,27 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2076,33 +2066,30 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2145,19 +2132,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2166,9 +2153,6 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2193,19 +2177,19 @@
         <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2217,25 +2201,85 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2249,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2305,50 +2349,45 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Johnny Furphy</t>
+          <t>Tony Bradley</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Tony Bradley</t>
+          <t>Isaiah Jackson</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Isaiah Jackson</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Jay Huff</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
@@ -2396,27 +2435,24 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2462,27 +2498,24 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2525,30 +2558,27 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2591,30 +2621,27 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>8</v>
       </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2657,32 +2684,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2720,33 +2744,30 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="n">
-        <v>8</v>
-      </c>
       <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2786,33 +2807,30 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2852,33 +2870,30 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2918,35 +2933,32 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
       </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2984,33 +2996,30 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
-      </c>
-      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3050,33 +3059,30 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3101,49 +3107,109 @@
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3157,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3213,50 +3279,45 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Johnny Furphy</t>
+          <t>Tony Bradley</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Tony Bradley</t>
+          <t>Isaiah Jackson</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Isaiah Jackson</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Jay Huff</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
@@ -3307,24 +3368,21 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3373,24 +3431,21 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3439,24 +3494,21 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3505,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3517,12 +3569,9 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3571,24 +3620,21 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3628,33 +3674,30 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3694,33 +3737,30 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3769,24 +3809,21 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3835,24 +3872,21 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3907,18 +3941,15 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3967,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -3979,12 +4010,9 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4018,10 +4046,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -4033,13 +4061,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -4050,8 +4078,68 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4065,7 +4153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4097,7 +4185,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.09090909090909</v>
+        <v>24.58333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -4107,7 +4195,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -4133,31 +4221,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.8</v>
+        <v>10.15384615384615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.09090909090909</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -4167,7 +4255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.25</v>
+        <v>8.076923076923077</v>
       </c>
     </row>
     <row r="11">
@@ -4177,7 +4265,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.909090909090909</v>
+        <v>6.538461538461538</v>
       </c>
     </row>
     <row r="12">
@@ -4187,7 +4275,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5.818181818181818</v>
       </c>
     </row>
     <row r="13">
@@ -4197,27 +4285,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.833333333333333</v>
+        <v>5.769230769230769</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.454545454545454</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.333333333333333</v>
+        <v>5.461538461538462</v>
       </c>
     </row>
     <row r="16">
@@ -4227,7 +4315,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.333333333333333</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -4247,17 +4335,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.875</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cody Martin</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.75</v>
+        <v>2.222222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -4271,7 +4349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4293,7 +4371,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
@@ -4303,7 +4381,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.272727272727272</v>
+        <v>5.083333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -4323,47 +4401,47 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.363636363636364</v>
+        <v>3.153846153846154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RayJ Dennis</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.666666666666667</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monté Morris</t>
+          <t>RayJ Dennis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.333333333333333</v>
+        <v>2.272727272727273</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>Monté Morris</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.727272727272727</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
@@ -4379,90 +4457,80 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aaron Nesmith</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.545454545454545</v>
+        <v>1.615384615384615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jeremiah Robinson-Earl</t>
+          <t>Aaron Nesmith</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.166666666666667</v>
+        <v>1.545454545454545</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T.J. McConnell</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Isaiah Jackson</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isaiah Jackson</t>
+          <t>Jeremiah Robinson-Earl</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Tony Bradley</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tony Bradley</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.75</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Johnny Furphy</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4477,7 +4545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4499,7 +4567,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.363636363636363</v>
+        <v>7.083333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -4529,7 +4597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.333333333333333</v>
+        <v>6.375</v>
       </c>
     </row>
     <row r="6">
@@ -4539,7 +4607,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.083333333333333</v>
+        <v>6.076923076923077</v>
       </c>
     </row>
     <row r="7">
@@ -4549,7 +4617,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.272727272727272</v>
+        <v>5.384615384615385</v>
       </c>
     </row>
     <row r="8">
@@ -4559,7 +4627,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.545454545454546</v>
+        <v>4.538461538461538</v>
       </c>
     </row>
     <row r="9">
@@ -4575,11 +4643,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Quenton Jackson</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -4589,63 +4657,63 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5</v>
+        <v>3.307692307692307</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quenton Jackson</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4</v>
+        <v>3.076923076923077</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.363636363636364</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RayJ Dennis</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1.833333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Johnny Furphy</t>
+          <t>RayJ Dennis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1.727272727272727</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Monté Morris</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.666666666666667</v>
+        <v>1.555555555555556</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Monté Morris</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4655,20 +4723,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>T.J. McConnell</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.375</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T.J. McConnell</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4683,7 +4741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4721,31 +4779,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jarace Walker</t>
+          <t>Andrew Nembhard</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.636363636363636</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andrew Nembhard</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.6</v>
+        <v>1.833333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pascal Siakam</t>
+          <t>Jarace Walker</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.545454545454545</v>
+        <v>1.384615384615385</v>
       </c>
     </row>
     <row r="7">
@@ -4765,7 +4823,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.111111111111111</v>
+        <v>1.090909090909091</v>
       </c>
     </row>
     <row r="9">
@@ -4785,7 +4843,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4795,13 +4853,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Monté Morris</t>
+          <t>Johnny Furphy</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4811,21 +4869,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Johnny Furphy</t>
+          <t>Taelon Peter</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taelon Peter</t>
+          <t>Monté Morris</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -4835,7 +4893,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="16">
@@ -4845,13 +4903,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cody Martin</t>
+          <t>Tony Bradley</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4861,20 +4919,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tony Bradley</t>
+          <t>Isaiah Jackson</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Isaiah Jackson</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4889,7 +4937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5219,27 @@
         <v>231</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>111</v>
+      </c>
+      <c r="D14" t="n">
+        <v>129</v>
+      </c>
+      <c r="E14" t="n">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
